--- a/data/input-sheet.xlsx
+++ b/data/input-sheet.xlsx
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="142">
   <si>
     <t xml:space="preserve">資産ダッシュボード 入力シート</t>
   </si>
@@ -1397,6 +1397,9 @@
     <t xml:space="preserve">円換算した評価額</t>
   </si>
   <si>
+    <t xml:space="preserve">円換算した取得原価</t>
+  </si>
+  <si>
     <t xml:space="preserve">国内</t>
   </si>
   <si>
@@ -1659,7 +1662,7 @@
     <t xml:space="preserve">　うち含み損益</t>
   </si>
   <si>
-    <t xml:space="preserve">評価額 − 取得原価</t>
+    <t xml:space="preserve">円換算した評価額 − 円換算した取得原価</t>
   </si>
   <si>
     <t xml:space="preserve">預貯金</t>
@@ -3185,7 +3188,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -3194,7 +3197,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3237,13 +3240,16 @@
       <c r="H5" s="21" t="s">
         <v>75</v>
       </c>
+      <c r="I5" s="21" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>34</v>
@@ -3263,13 +3269,17 @@
         <f aca="false">ROUND(E6*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C6,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>5000000</v>
       </c>
+      <c r="I6" s="28" t="n">
+        <f aca="false">ROUND(D6*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C6,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>2000000</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>34</v>
@@ -3289,13 +3299,17 @@
         <f aca="false">ROUND(E7*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C7,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>2500000</v>
       </c>
+      <c r="I7" s="28" t="n">
+        <f aca="false">ROUND(D7*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C7,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>2700000</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>34</v>
@@ -3315,13 +3329,17 @@
         <f aca="false">ROUND(E8*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C8,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>1500000</v>
       </c>
+      <c r="I8" s="28" t="n">
+        <f aca="false">ROUND(D8*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C8,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>1300000</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>34</v>
@@ -3333,7 +3351,7 @@
         <v>1200000</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">E9-D9</f>
@@ -3343,13 +3361,17 @@
         <f aca="false">ROUND(E9*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C9,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>1200000</v>
       </c>
+      <c r="I9" s="28" t="n">
+        <f aca="false">ROUND(D9*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C9,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>800000</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>36</v>
@@ -3369,13 +3391,17 @@
         <f aca="false">ROUND(E10*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C10,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>4966400</v>
       </c>
+      <c r="I10" s="28" t="n">
+        <f aca="false">ROUND(D10*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C10,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>3104000</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>36</v>
@@ -3395,13 +3421,17 @@
         <f aca="false">ROUND(E11*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C11,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>2483200</v>
       </c>
+      <c r="I11" s="28" t="n">
+        <f aca="false">ROUND(D11*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C11,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>2793600</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>36</v>
@@ -3421,13 +3451,17 @@
         <f aca="false">ROUND(E12*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C12,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>1474400</v>
       </c>
+      <c r="I12" s="28" t="n">
+        <f aca="false">ROUND(D12*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C12,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>1241600</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>36</v>
@@ -3439,7 +3473,7 @@
         <v>11000</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G13" s="28" t="n">
         <f aca="false">E13-D13</f>
@@ -3449,10 +3483,14 @@
         <f aca="false">ROUND(E13*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C13,基本情報!$A$10:$A$13,0)),0),0)</f>
         <v>1707200</v>
       </c>
+      <c r="I13" s="28" t="n">
+        <f aca="false">ROUND(D13*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C13,基本情報!$A$10:$A$13,0)),0),0)</f>
+        <v>776000</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">SUM(D6:D13)</f>
@@ -3463,7 +3501,7 @@
         <v>10268500</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G14" s="31" t="n">
         <f aca="false">SUM(G6:G13)</f>
@@ -3472,6 +3510,10 @@
       <c r="H14" s="31" t="n">
         <f aca="false">SUM(H6:H13)</f>
         <v>20831200</v>
+      </c>
+      <c r="I14" s="31" t="n">
+        <f aca="false">SUM(I6:I13)</f>
+        <v>14715200</v>
       </c>
     </row>
   </sheetData>
@@ -3508,31 +3550,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>34</v>
@@ -3673,7 +3715,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">SUM(D6:D19)</f>
@@ -3716,22 +3758,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>70</v>
@@ -3752,18 +3794,18 @@
         <v>52</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>3000000</v>
@@ -3925,70 +3967,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">有価証券!H14</f>
         <v>20831200</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" s="28" t="n">
-        <f aca="false">有価証券!H14-SUMPRODUCT(有価証券!D6:D13,IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(有価証券!C6:C13,基本情報!$A$10:$A$13,0)),0))</f>
+        <f aca="false">有価証券!H14-有価証券!I14</f>
         <v>6116000</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">預貯金!D20</f>
         <v>0</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" s="33" t="n">
         <f aca="false">有価証券!H14+預貯金!D20</f>
         <v>20831200</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4000,12 +4042,12 @@
         <v>0</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="28" t="n">
         <f aca="false">SUM(不動産!$F$6:$F$14)</f>
@@ -4015,19 +4057,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="28" t="n">
         <f aca="false">SUM(不動産!$G$6:$G$14)</f>
         <v>0</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B14" s="28" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)</f>
@@ -4044,41 +4086,41 @@
         <v>0</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" s="34" t="n">
         <f aca="false">IFERROR(SUM(不動産!$R$6:$R$14)/SUM(不動産!$G$6:$G$14),0)</f>
         <v>0</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">SUM(不動産!$T$6:$T$14)</f>
         <v>0</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B20" s="28" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)</f>
@@ -4088,96 +4130,96 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B22" s="33" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*(不動産!H6:H14&gt;不動産!G6:G14))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B28" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT((その他の借入!A7:A15&lt;&gt;"")*(その他の借入!E7:E15&gt;その他の借入!D7:D15))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B29" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!F6:H14&lt;0)*1)+SUMPRODUCT((有価証券!D6:E13&lt;0)*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B30" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT(ISERROR(MATCH(有価証券!C6:C13,基本情報!$A$10:$A$13,0))*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B31" s="35" t="str">
         <f aca="false">IF(OR(基本情報!B4="",基本情報!B5=""),"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/data/input-sheet.xlsx
+++ b/data/input-sheet.xlsx
@@ -13,8 +13,9 @@
     <sheet name="不動産" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="有価証券" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="預貯金" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="その他の借入" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="検算" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="保険" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="その他の借入" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="検算" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -43,7 +44,147 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0">
+    <comment ref="K4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">契約したときの期間です（残りの期間ではありません）。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">26</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">11</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">か月なら「年」に </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">26</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">、「か月」に </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">11</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">。ちょうど</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">20</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年なら </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">20 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">と </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">。返済回数しか分からないときは </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">12 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">で割った商と余りを入れてください。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,8 +286,42 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">これまでに払った保険料の合計です。取得原価にあたります。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">解約返戻金が「いつ時点」の数字かを入れます。基準日とズレていて構いません（画面にそのまま出ます）。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="168">
   <si>
     <t xml:space="preserve">資産ダッシュボード 入力シート</t>
   </si>
@@ -945,13 +1120,126 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">当初</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">年</t>
     </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">借入期間</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">当初</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">毎月の返済額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家賃収入</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -960,9 +1248,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">毎月の返済額</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -971,7 +1256,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">家賃収入</t>
+      <t xml:space="preserve">管理費</t>
     </r>
     <r>
       <rPr>
@@ -1015,7 +1300,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">管理費</t>
+      <t xml:space="preserve">修繕積立金</t>
     </r>
     <r>
       <rPr>
@@ -1059,7 +1344,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">修繕積立金</t>
+      <t xml:space="preserve">固定資産税</t>
     </r>
     <r>
       <rPr>
@@ -1080,6 +1365,56 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">年額</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">総投資額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計返済額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固定資産税</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">月</t>
     </r>
     <r>
@@ -1095,6 +1430,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">月次収支</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1103,7 +1441,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">固定資産税</t>
+      <t xml:space="preserve">借入期間 合計</t>
     </r>
     <r>
       <rPr>
@@ -1124,7 +1462,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年額</t>
+      <t xml:space="preserve">か月</t>
     </r>
     <r>
       <rPr>
@@ -1137,59 +1475,6 @@
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">総投資額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計返済額</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">固定資産税</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">月次収支</t>
   </si>
   <si>
     <r>
@@ -1561,7 +1846,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不動産以外の借入　（</t>
+      <t xml:space="preserve">保険　（</t>
     </r>
     <r>
       <rPr>
@@ -1599,26 +1884,92 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">つのローン）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">車のローン、教育ローン、多目的ローンなど。不動産のローンは「不動産」タブに書くので、ここには書きません。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">借入がなければ、すべて空のままで構いません。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">借入の名前</t>
-  </si>
-  <si>
-    <t xml:space="preserve">返済済み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（例）自動車ローン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車</t>
+      <t xml:space="preserve">つの契約）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">貯蓄性のある保険（終身・養老・個人年金など）を書きます。掛け捨ての医療保険などは書きません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">評価額には「解約返戻金」（今解約したら戻る額）を入れます。毎年届く「ご契約内容のお知らせ」か保険会社のマイページで分かります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 死亡保険金額は参考です。今使えるお金ではないので、資産の合計には足しません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保険名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保険会社</t>
+  </si>
+  <si>
+    <t xml:space="preserve">払込保険料 累計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解約返戻金</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">死亡保険金額
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考・資産に含めず</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">評価日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した解約返戻金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した払込保険料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（例）変額終身保険</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○○生命</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-31</t>
   </si>
   <si>
     <r>
@@ -1626,79 +1977,32 @@
         <i val="true"/>
         <sz val="10"/>
         <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">解約返戻金は年</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="10"/>
         <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">銀行</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">検算　（自動計算。送る前にここを見てください）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この表はすべて自動です。画面に出る数字と同じものを先に確かめられます。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金融資産</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有価証券（評価額・円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円換算した評価額の合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　うち含み損益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円換算した評価額 − 円換算した取得原価</t>
-  </si>
-  <si>
-    <t xml:space="preserve">預貯金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円換算した残高の合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金融資産合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有価証券 ＋ 預貯金（不動産は含めません）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不動産</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自己資金 ＋ 当初借入額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自己資金累計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">借入総額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当初の借入額の合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残債合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">借入総額 − 残債合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">返済進捗率</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回の通知の数字</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1708,7 +2012,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">累計返済額 </t>
+      <t xml:space="preserve">※ 解約返戻金がまだ分からないときは、払込保険料累計と同じ額を入れ、「補足」に「解約返戻金 未確認（暫定）」と書いてください。含み損益は </t>
     </r>
     <r>
       <rPr>
@@ -1718,7 +2022,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">÷ </t>
+      <t xml:space="preserve">±0 </t>
     </r>
     <r>
       <rPr>
@@ -1727,53 +2031,167 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">借入総額</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">月次収支の合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">家賃 − 返済 − 経費。マイナスなら持ち出しです</t>
-  </si>
-  <si>
-    <t xml:space="preserve">負債</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不動産ローン 残債</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その他の借入 残債</t>
-  </si>
-  <si>
-    <t xml:space="preserve">車・多目的など</t>
-  </si>
-  <si>
-    <t xml:space="preserve">総負債</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不動産 ＋ その他</t>
-  </si>
-  <si>
-    <t xml:space="preserve">つじつまの確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「要確認」が出たら、その行の説明どおりに直してください。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残債が当初借入額より大きい物件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残債は当初借入額以下になるはずです</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残債が当初借入額より大きい借入</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マイナスの金額が入っている</t>
+      <t xml:space="preserve">になります。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不動産以外の借入　（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行に</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つのローン）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">車のローン、教育ローン、多目的ローンなど。不動産のローンは「不動産」タブに書くので、ここには書きません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">借入がなければ、すべて空のままで構いません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">借入の名前</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返済済み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（例）自動車ローン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">銀行</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">検算　（自動計算。送る前にここを見てください）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この表はすべて自動です。画面に出る数字と同じものを先に確かめられます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金融資産</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有価証券（評価額・円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した評価額の合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　うち含み損益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した評価額 − 円換算した取得原価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保険（解約返戻金・円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死亡保険金額は含めません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解約返戻金 − 払込保険料（保障の対価を含む）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">預貯金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した残高の合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金融資産合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有価証券 ＋ 保険 ＋ 預貯金（不動産は含めません）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面のサマリーに出る数字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不動産</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自己資金 ＋ 当初借入額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自己資金累計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">借入総額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の借入額の合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残債合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">借入総額 − 残債合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返済進捗率</t>
   </si>
   <si>
     <r>
@@ -1783,7 +2201,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">金額はすべて </t>
+      <t xml:space="preserve">累計返済額 </t>
     </r>
     <r>
       <rPr>
@@ -1793,7 +2211,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0 </t>
+      <t xml:space="preserve">÷ </t>
     </r>
     <r>
       <rPr>
@@ -1802,6 +2220,81 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">借入総額</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">月次収支の合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">家賃 − 返済 − 経費。マイナスなら持ち出しです</t>
+  </si>
+  <si>
+    <t xml:space="preserve">負債</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不動産ローン 残債</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他の借入 残債</t>
+  </si>
+  <si>
+    <t xml:space="preserve">車・多目的など</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総負債</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不動産 ＋ その他</t>
+  </si>
+  <si>
+    <t xml:space="preserve">つじつまの確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「要確認」が出たら、その行の説明どおりに直してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残債が当初借入額より大きい物件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残債は当初借入額以下になるはずです</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残債が当初借入額より大きい借入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マイナスの金額が入っている</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金額はすべて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">以上で入れます</t>
     </r>
   </si>
@@ -1816,6 +2309,74 @@
   </si>
   <si>
     <t xml:space="preserve">どちらも必須です</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">借入期間の「か月」が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月以上は「年」の側に繰り上げてください</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">保険にレートの無い通貨がある</t>
   </si>
 </sst>
 </file>
@@ -2046,7 +2607,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2189,6 +2750,10 @@
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2700,7 +3265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -2711,15 +3276,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2793,19 +3359,25 @@
       <c r="T4" s="21" t="s">
         <v>60</v>
       </c>
+      <c r="U4" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>45.5</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>15</v>
@@ -2820,44 +3392,51 @@
         <v>35500000</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>1.8</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="L5" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="M5" s="24" t="n">
         <v>128000</v>
       </c>
-      <c r="M5" s="24" t="n">
+      <c r="N5" s="24" t="n">
         <v>180000</v>
       </c>
-      <c r="N5" s="24" t="n">
+      <c r="O5" s="24" t="n">
         <v>12000</v>
       </c>
-      <c r="O5" s="24" t="n">
+      <c r="P5" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="P5" s="24" t="n">
+      <c r="Q5" s="24" t="n">
         <v>108000</v>
       </c>
-      <c r="Q5" s="24" t="n">
+      <c r="R5" s="24" t="n">
         <f aca="false">F5+G5</f>
         <v>50000000</v>
       </c>
-      <c r="R5" s="24" t="n">
+      <c r="S5" s="24" t="n">
         <f aca="false">G5-H5</f>
         <v>4500000</v>
       </c>
-      <c r="S5" s="24" t="n">
-        <f aca="false">ROUND(P5/12,0)</f>
+      <c r="T5" s="24" t="n">
+        <f aca="false">ROUND(Q5/12,0)</f>
         <v>9000</v>
       </c>
-      <c r="T5" s="24" t="n">
-        <f aca="false">M5-L5-N5-O5-S5</f>
+      <c r="U5" s="24" t="n">
+        <f aca="false">N5-M5-O5-P5-T5</f>
         <v>23000</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <f aca="false">K5*12+L5</f>
+        <v>323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2872,25 +3451,30 @@
       <c r="I6" s="19"/>
       <c r="J6" s="27"/>
       <c r="K6" s="19"/>
-      <c r="L6" s="26"/>
+      <c r="L6" s="19"/>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
       <c r="O6" s="26"/>
       <c r="P6" s="26"/>
-      <c r="Q6" s="28" t="n">
+      <c r="Q6" s="26"/>
+      <c r="R6" s="28" t="n">
         <f aca="false">F6+G6</f>
         <v>0</v>
       </c>
-      <c r="R6" s="28" t="n">
+      <c r="S6" s="28" t="n">
         <f aca="false">G6-H6</f>
         <v>0</v>
       </c>
-      <c r="S6" s="28" t="n">
-        <f aca="false">ROUND(P6/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T6" s="28" t="n">
-        <f aca="false">M6-L6-N6-O6-S6</f>
+        <f aca="false">ROUND(Q6/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="28" t="n">
+        <f aca="false">N6-M6-O6-P6-T6</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="17" t="n">
+        <f aca="false">K6*12+L6</f>
         <v>0</v>
       </c>
     </row>
@@ -2906,25 +3490,30 @@
       <c r="I7" s="19"/>
       <c r="J7" s="27"/>
       <c r="K7" s="19"/>
-      <c r="L7" s="26"/>
+      <c r="L7" s="19"/>
       <c r="M7" s="26"/>
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
       <c r="P7" s="26"/>
-      <c r="Q7" s="28" t="n">
+      <c r="Q7" s="26"/>
+      <c r="R7" s="28" t="n">
         <f aca="false">F7+G7</f>
         <v>0</v>
       </c>
-      <c r="R7" s="28" t="n">
+      <c r="S7" s="28" t="n">
         <f aca="false">G7-H7</f>
         <v>0</v>
       </c>
-      <c r="S7" s="28" t="n">
-        <f aca="false">ROUND(P7/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T7" s="28" t="n">
-        <f aca="false">M7-L7-N7-O7-S7</f>
+        <f aca="false">ROUND(Q7/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="28" t="n">
+        <f aca="false">N7-M7-O7-P7-T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="17" t="n">
+        <f aca="false">K7*12+L7</f>
         <v>0</v>
       </c>
     </row>
@@ -2940,25 +3529,30 @@
       <c r="I8" s="19"/>
       <c r="J8" s="27"/>
       <c r="K8" s="19"/>
-      <c r="L8" s="26"/>
+      <c r="L8" s="19"/>
       <c r="M8" s="26"/>
       <c r="N8" s="26"/>
       <c r="O8" s="26"/>
       <c r="P8" s="26"/>
-      <c r="Q8" s="28" t="n">
+      <c r="Q8" s="26"/>
+      <c r="R8" s="28" t="n">
         <f aca="false">F8+G8</f>
         <v>0</v>
       </c>
-      <c r="R8" s="28" t="n">
+      <c r="S8" s="28" t="n">
         <f aca="false">G8-H8</f>
         <v>0</v>
       </c>
-      <c r="S8" s="28" t="n">
-        <f aca="false">ROUND(P8/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T8" s="28" t="n">
-        <f aca="false">M8-L8-N8-O8-S8</f>
+        <f aca="false">ROUND(Q8/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="28" t="n">
+        <f aca="false">N8-M8-O8-P8-T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="17" t="n">
+        <f aca="false">K8*12+L8</f>
         <v>0</v>
       </c>
     </row>
@@ -2974,25 +3568,30 @@
       <c r="I9" s="19"/>
       <c r="J9" s="27"/>
       <c r="K9" s="19"/>
-      <c r="L9" s="26"/>
+      <c r="L9" s="19"/>
       <c r="M9" s="26"/>
       <c r="N9" s="26"/>
       <c r="O9" s="26"/>
       <c r="P9" s="26"/>
-      <c r="Q9" s="28" t="n">
+      <c r="Q9" s="26"/>
+      <c r="R9" s="28" t="n">
         <f aca="false">F9+G9</f>
         <v>0</v>
       </c>
-      <c r="R9" s="28" t="n">
+      <c r="S9" s="28" t="n">
         <f aca="false">G9-H9</f>
         <v>0</v>
       </c>
-      <c r="S9" s="28" t="n">
-        <f aca="false">ROUND(P9/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T9" s="28" t="n">
-        <f aca="false">M9-L9-N9-O9-S9</f>
+        <f aca="false">ROUND(Q9/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="28" t="n">
+        <f aca="false">N9-M9-O9-P9-T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="17" t="n">
+        <f aca="false">K9*12+L9</f>
         <v>0</v>
       </c>
     </row>
@@ -3008,25 +3607,30 @@
       <c r="I10" s="19"/>
       <c r="J10" s="27"/>
       <c r="K10" s="19"/>
-      <c r="L10" s="26"/>
+      <c r="L10" s="19"/>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
       <c r="O10" s="26"/>
       <c r="P10" s="26"/>
-      <c r="Q10" s="28" t="n">
+      <c r="Q10" s="26"/>
+      <c r="R10" s="28" t="n">
         <f aca="false">F10+G10</f>
         <v>0</v>
       </c>
-      <c r="R10" s="28" t="n">
+      <c r="S10" s="28" t="n">
         <f aca="false">G10-H10</f>
         <v>0</v>
       </c>
-      <c r="S10" s="28" t="n">
-        <f aca="false">ROUND(P10/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T10" s="28" t="n">
-        <f aca="false">M10-L10-N10-O10-S10</f>
+        <f aca="false">ROUND(Q10/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="28" t="n">
+        <f aca="false">N10-M10-O10-P10-T10</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="17" t="n">
+        <f aca="false">K10*12+L10</f>
         <v>0</v>
       </c>
     </row>
@@ -3042,25 +3646,30 @@
       <c r="I11" s="19"/>
       <c r="J11" s="27"/>
       <c r="K11" s="19"/>
-      <c r="L11" s="26"/>
+      <c r="L11" s="19"/>
       <c r="M11" s="26"/>
       <c r="N11" s="26"/>
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
-      <c r="Q11" s="28" t="n">
+      <c r="Q11" s="26"/>
+      <c r="R11" s="28" t="n">
         <f aca="false">F11+G11</f>
         <v>0</v>
       </c>
-      <c r="R11" s="28" t="n">
+      <c r="S11" s="28" t="n">
         <f aca="false">G11-H11</f>
         <v>0</v>
       </c>
-      <c r="S11" s="28" t="n">
-        <f aca="false">ROUND(P11/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T11" s="28" t="n">
-        <f aca="false">M11-L11-N11-O11-S11</f>
+        <f aca="false">ROUND(Q11/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="28" t="n">
+        <f aca="false">N11-M11-O11-P11-T11</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="17" t="n">
+        <f aca="false">K11*12+L11</f>
         <v>0</v>
       </c>
     </row>
@@ -3076,25 +3685,30 @@
       <c r="I12" s="19"/>
       <c r="J12" s="27"/>
       <c r="K12" s="19"/>
-      <c r="L12" s="26"/>
+      <c r="L12" s="19"/>
       <c r="M12" s="26"/>
       <c r="N12" s="26"/>
       <c r="O12" s="26"/>
       <c r="P12" s="26"/>
-      <c r="Q12" s="28" t="n">
+      <c r="Q12" s="26"/>
+      <c r="R12" s="28" t="n">
         <f aca="false">F12+G12</f>
         <v>0</v>
       </c>
-      <c r="R12" s="28" t="n">
+      <c r="S12" s="28" t="n">
         <f aca="false">G12-H12</f>
         <v>0</v>
       </c>
-      <c r="S12" s="28" t="n">
-        <f aca="false">ROUND(P12/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T12" s="28" t="n">
-        <f aca="false">M12-L12-N12-O12-S12</f>
+        <f aca="false">ROUND(Q12/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="28" t="n">
+        <f aca="false">N12-M12-O12-P12-T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="17" t="n">
+        <f aca="false">K12*12+L12</f>
         <v>0</v>
       </c>
     </row>
@@ -3110,25 +3724,30 @@
       <c r="I13" s="19"/>
       <c r="J13" s="27"/>
       <c r="K13" s="19"/>
-      <c r="L13" s="26"/>
+      <c r="L13" s="19"/>
       <c r="M13" s="26"/>
       <c r="N13" s="26"/>
       <c r="O13" s="26"/>
       <c r="P13" s="26"/>
-      <c r="Q13" s="28" t="n">
+      <c r="Q13" s="26"/>
+      <c r="R13" s="28" t="n">
         <f aca="false">F13+G13</f>
         <v>0</v>
       </c>
-      <c r="R13" s="28" t="n">
+      <c r="S13" s="28" t="n">
         <f aca="false">G13-H13</f>
         <v>0</v>
       </c>
-      <c r="S13" s="28" t="n">
-        <f aca="false">ROUND(P13/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T13" s="28" t="n">
-        <f aca="false">M13-L13-N13-O13-S13</f>
+        <f aca="false">ROUND(Q13/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="28" t="n">
+        <f aca="false">N13-M13-O13-P13-T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <f aca="false">K13*12+L13</f>
         <v>0</v>
       </c>
     </row>
@@ -3144,31 +3763,36 @@
       <c r="I14" s="19"/>
       <c r="J14" s="27"/>
       <c r="K14" s="19"/>
-      <c r="L14" s="26"/>
+      <c r="L14" s="19"/>
       <c r="M14" s="26"/>
       <c r="N14" s="26"/>
       <c r="O14" s="26"/>
       <c r="P14" s="26"/>
-      <c r="Q14" s="28" t="n">
+      <c r="Q14" s="26"/>
+      <c r="R14" s="28" t="n">
         <f aca="false">F14+G14</f>
         <v>0</v>
       </c>
-      <c r="R14" s="28" t="n">
+      <c r="S14" s="28" t="n">
         <f aca="false">G14-H14</f>
         <v>0</v>
       </c>
-      <c r="S14" s="28" t="n">
-        <f aca="false">ROUND(P14/12,0)</f>
-        <v>0</v>
-      </c>
       <c r="T14" s="28" t="n">
-        <f aca="false">M14-L14-N14-O14-S14</f>
+        <f aca="false">ROUND(Q14/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="28" t="n">
+        <f aca="false">N14-M14-O14-P14-T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="17" t="n">
+        <f aca="false">K14*12+L14</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3202,54 +3826,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>34</v>
@@ -3276,10 +3900,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>34</v>
@@ -3306,10 +3930,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>34</v>
@@ -3336,10 +3960,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>34</v>
@@ -3351,7 +3975,7 @@
         <v>1200000</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">E9-D9</f>
@@ -3368,10 +3992,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>36</v>
@@ -3398,10 +4022,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>36</v>
@@ -3428,10 +4052,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>36</v>
@@ -3458,10 +4082,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>83</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>81</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>36</v>
@@ -3473,7 +4097,7 @@
         <v>11000</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G13" s="28" t="n">
         <f aca="false">E13-D13</f>
@@ -3490,7 +4114,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">SUM(D6:D13)</f>
@@ -3501,7 +4125,7 @@
         <v>10268500</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G14" s="31" t="n">
         <f aca="false">SUM(G6:G13)</f>
@@ -3550,31 +4174,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>34</v>
@@ -3715,7 +4339,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">SUM(D6:D19)</f>
@@ -3744,6 +4368,308 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <f aca="false">IF(A7="","",E7-D7)</f>
+        <v>-400000</v>
+      </c>
+      <c r="J7" s="24" t="n">
+        <f aca="false">IF(A7="","",ROUND(E7*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C7,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v>2600000</v>
+      </c>
+      <c r="K7" s="24" t="n">
+        <f aca="false">IF(A7="","",ROUND(D7*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C7,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="28" t="str">
+        <f aca="false">IF(A8="","",E8-D8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="28" t="str">
+        <f aca="false">IF(A8="","",ROUND(E8*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C8,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+      <c r="K8" s="28" t="str">
+        <f aca="false">IF(A8="","",ROUND(D8*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C8,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="28" t="str">
+        <f aca="false">IF(A9="","",E9-D9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="28" t="str">
+        <f aca="false">IF(A9="","",ROUND(E9*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C9,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+      <c r="K9" s="28" t="str">
+        <f aca="false">IF(A9="","",ROUND(D9*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C9,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="28" t="str">
+        <f aca="false">IF(A10="","",E10-D10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="28" t="str">
+        <f aca="false">IF(A10="","",ROUND(E10*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C10,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+      <c r="K10" s="28" t="str">
+        <f aca="false">IF(A10="","",ROUND(D10*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C10,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="28" t="str">
+        <f aca="false">IF(A11="","",E11-D11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="28" t="str">
+        <f aca="false">IF(A11="","",ROUND(E11*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C11,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+      <c r="K11" s="28" t="str">
+        <f aca="false">IF(A11="","",ROUND(D11*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C11,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="28" t="str">
+        <f aca="false">IF(A12="","",E12-D12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="28" t="str">
+        <f aca="false">IF(A12="","",ROUND(E12*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C12,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+      <c r="K12" s="28" t="str">
+        <f aca="false">IF(A12="","",ROUND(D12*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C12,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="28" t="str">
+        <f aca="false">IF(A13="","",E13-D13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="28" t="str">
+        <f aca="false">IF(A13="","",ROUND(E13*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C13,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+      <c r="K13" s="28" t="str">
+        <f aca="false">IF(A13="","",ROUND(D13*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C13,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="28" t="str">
+        <f aca="false">IF(A14="","",E14-D14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="28" t="str">
+        <f aca="false">IF(A14="","",ROUND(E14*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C14,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+      <c r="K14" s="28" t="str">
+        <f aca="false">IF(A14="","",ROUND(D14*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(C14,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="31" t="n">
+        <f aca="false">SUM(J8:J14)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="31" t="n">
+        <f aca="false">SUM(K8:K14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C7:C14" type="list">
+      <formula1>"JPY,USD,EUR"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3758,25 +4684,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>49</v>
@@ -3791,21 +4717,21 @@
         <v>50</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>3000000</v>
@@ -3952,12 +4878,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3967,263 +4893,323 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">有価証券!H14</f>
         <v>20831200</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B6" s="28" t="n">
         <f aca="false">有価証券!H14-有価証券!I14</f>
         <v>6116000</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B7" s="28" t="n">
+        <f aca="false">保険!J15</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="28" t="n">
+        <f aca="false">保険!J15-保険!K15</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="28" t="n">
         <f aca="false">預貯金!D20</f>
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="33" t="n">
-        <f aca="false">有価証券!H14+預貯金!D20</f>
+      <c r="C9" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="33" t="n">
+        <f aca="false">有価証券!H14+保険!J15+預貯金!D20</f>
         <v>20831200</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>113</v>
+      <c r="C10" s="15" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="B11" s="28" t="n">
-        <f aca="false">SUM(不動産!$Q$6:$Q$14)</f>
-        <v>0</v>
+        <f aca="false">有価証券!H14+保険!J15-有価証券!I14-保険!K15</f>
+        <v>6116000</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="28" t="n">
-        <f aca="false">SUM(不動産!$F$6:$F$14)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="15"/>
+        <v>135</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B13" s="28" t="n">
-        <f aca="false">SUM(不動産!$G$6:$G$14)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>117</v>
+      <c r="A13" s="14" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="B14" s="28" t="n">
-        <f aca="false">SUM(不動産!$H$6:$H$14)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="15"/>
+        <f aca="false">SUM(不動産!$R$6:$R$14)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="B15" s="28" t="n">
-        <f aca="false">SUM(不動産!$R$6:$R$14)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>119</v>
-      </c>
+        <f aca="false">SUM(不動産!$F$6:$F$14)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="34" t="n">
-        <f aca="false">IFERROR(SUM(不動産!$R$6:$R$14)/SUM(不動産!$G$6:$G$14),0)</f>
+        <v>139</v>
+      </c>
+      <c r="B16" s="28" t="n">
+        <f aca="false">SUM(不動産!$G$6:$G$14)</f>
         <v>0</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="B17" s="28" t="n">
-        <f aca="false">SUM(不動産!$T$6:$T$14)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>123</v>
+        <f aca="false">SUM(不動産!$H$6:$H$14)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="28" t="n">
+        <f aca="false">SUM(不動産!$S$6:$S$14)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>124</v>
+      <c r="A19" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="34" t="n">
+        <f aca="false">IFERROR(SUM(不動産!$S$6:$S$14)/SUM(不動産!$G$6:$G$14),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="B20" s="28" t="n">
+        <f aca="false">SUM(不動産!$U$6:$U$14)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="28" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="28" t="n">
+      <c r="C23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="28" t="n">
         <f aca="false">SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="B22" s="33" t="n">
+      <c r="C24" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="33" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B27" s="35" t="str">
+      <c r="C25" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*(不動産!H6:H14&gt;不動産!G6:G14))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B28" s="35" t="str">
+      <c r="C30" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT((その他の借入!A7:A15&lt;&gt;"")*(その他の借入!E7:E15&gt;その他の借入!D7:D15))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B29" s="35" t="str">
+      <c r="C31" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!F6:H14&lt;0)*1)+SUMPRODUCT((有価証券!D6:E13&lt;0)*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="35" t="str">
+      <c r="C32" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="35" t="str">
         <f aca="false">IF(SUMPRODUCT(ISERROR(MATCH(有価証券!C6:C13,基本情報!$A$10:$A$13,0))*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="35" t="str">
+      <c r="C33" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="35" t="str">
         <f aca="false">IF(OR(基本情報!B4="",基本情報!B5=""),"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>141</v>
+      <c r="C34" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="35" t="str">
+        <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*((不動産!L6:L14&lt;0)+(不動産!L6:L14&gt;11)))&gt;0,"要確認","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="35" t="str">
+        <f aca="false">IF(SUMPRODUCT((保険!A8:A14&lt;&gt;"")*ISERROR(MATCH(保険!C8:C14,基本情報!$A$10:$A$13,0)))&gt;0,"要確認","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B27:B31">
+  <conditionalFormatting sqref="B30:B36">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"要確認"</formula>
     </cfRule>
